--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.6662362487217</v>
+        <v>6.770763390417277</v>
       </c>
       <c r="D2" t="n">
-        <v>41.72719500732859</v>
+        <v>6.780669188690896</v>
       </c>
       <c r="E2" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F2" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.78836516687105</v>
+        <v>7.278109339616545</v>
       </c>
       <c r="D3" t="n">
-        <v>44.28975122657511</v>
+        <v>7.197084574318455</v>
       </c>
       <c r="E3" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F3" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.25787941540886</v>
+        <v>5.404405405003939</v>
       </c>
       <c r="D4" t="n">
-        <v>32.81331502087651</v>
+        <v>5.332163690892433</v>
       </c>
       <c r="E4" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F4" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.4093950755999</v>
+        <v>3.641526699784984</v>
       </c>
       <c r="D5" t="n">
-        <v>21.87952564977769</v>
+        <v>3.555422918088874</v>
       </c>
       <c r="E5" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F5" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.312238374095226</v>
+        <v>0.8632387357904742</v>
       </c>
       <c r="D6" t="n">
-        <v>5.678024167679586</v>
+        <v>0.9226789272479328</v>
       </c>
       <c r="E6" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F6" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.81957084665896</v>
+        <v>5.00818026258208</v>
       </c>
       <c r="D7" t="n">
-        <v>30.63862202678256</v>
+        <v>4.978776079352166</v>
       </c>
       <c r="E7" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F7" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.00426032560533</v>
+        <v>3.413192302910866</v>
       </c>
       <c r="D8" t="n">
-        <v>13.0862523283024</v>
+        <v>2.12651600334914</v>
       </c>
       <c r="E8" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F8" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.32050810379712</v>
+        <v>4.277082566867032</v>
       </c>
       <c r="D9" t="n">
-        <v>18.59664404887678</v>
+        <v>3.021954657942476</v>
       </c>
       <c r="E9" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F9" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.30577402167997</v>
+        <v>7.524688278522994</v>
       </c>
       <c r="D10" t="n">
-        <v>37.08683937367955</v>
+        <v>6.026611398222927</v>
       </c>
       <c r="E10" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F10" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.63188095702952</v>
+        <v>8.227680655517299</v>
       </c>
       <c r="D11" t="n">
-        <v>50.70684008675555</v>
+        <v>8.239861514097777</v>
       </c>
       <c r="E11" t="n">
-        <v>13.29850518370509</v>
+        <v>2.161007092352077</v>
       </c>
       <c r="F11" t="n">
-        <v>13.78924325590293</v>
+        <v>2.240752029084226</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
